--- a/result/morris/morris_first_inf_ONLY_MAE_N256_seed2024.xlsx
+++ b/result/morris/morris_first_inf_ONLY_MAE_N256_seed2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,145 +453,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.43739149305555</v>
+        <v>-5.15266927083333</v>
       </c>
       <c r="C2" t="n">
-        <v>17.37858072916666</v>
+        <v>15.43435329861111</v>
       </c>
       <c r="D2" t="n">
-        <v>22.80727475920134</v>
+        <v>25.8315403362648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.57921006944445</v>
+        <v>1.507161458333334</v>
       </c>
       <c r="C3" t="n">
-        <v>16.82009548611112</v>
+        <v>13.93836805555557</v>
       </c>
       <c r="D3" t="n">
-        <v>23.90639022738969</v>
+        <v>26.03941014097901</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.88650173611112</v>
+        <v>2.359049479166666</v>
       </c>
       <c r="C4" t="n">
-        <v>16.12608506944445</v>
+        <v>11.40961371527778</v>
       </c>
       <c r="D4" t="n">
-        <v>25.26541607461052</v>
+        <v>17.9599408652448</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-7.421440972222226</v>
+        <v>2.840169270833334</v>
       </c>
       <c r="C5" t="n">
-        <v>16.033203125</v>
+        <v>10.31412760416666</v>
       </c>
       <c r="D5" t="n">
-        <v>25.40415572636949</v>
+        <v>15.36992369118523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sporulation__Tmax</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.276150173611111</v>
+        <v>1.717230902777777</v>
       </c>
       <c r="C6" t="n">
-        <v>4.992296006944445</v>
+        <v>7.671223958333339</v>
       </c>
       <c r="D6" t="n">
-        <v>12.73153184237543</v>
+        <v>12.66060772873587</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>sporulation__Tmax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.016818576388889</v>
+        <v>1.076822916666667</v>
       </c>
       <c r="C7" t="n">
-        <v>3.545898437500002</v>
+        <v>7.358940972222222</v>
       </c>
       <c r="D7" t="n">
-        <v>7.874548388479929</v>
+        <v>14.52288092128671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dispersal__wind_min</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5087890625</v>
+        <v>-1.111219618055556</v>
       </c>
       <c r="C8" t="n">
-        <v>2.912217881944445</v>
+        <v>5.403537326388888</v>
       </c>
       <c r="D8" t="n">
-        <v>9.028531621130995</v>
+        <v>13.4073787068432</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>dispersal__wind_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.0966796875</v>
+        <v>2.869249131944445</v>
       </c>
       <c r="C9" t="n">
-        <v>1.948893229166667</v>
+        <v>5.261610243055556</v>
       </c>
       <c r="D9" t="n">
-        <v>11.05007800258899</v>
+        <v>15.36257818475284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.045355902777778</v>
+        <v>-0.2558593749999999</v>
       </c>
       <c r="C10" t="n">
-        <v>1.73828125</v>
+        <v>2.620876736111111</v>
       </c>
       <c r="D10" t="n">
-        <v>8.225846644998713</v>
+        <v>7.564557267699343</v>
       </c>
     </row>
     <row r="11">
@@ -601,45 +601,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.296440972222222</v>
+        <v>-0.009765625000000062</v>
       </c>
       <c r="C11" t="n">
-        <v>1.470052083333333</v>
+        <v>1.546440972222222</v>
       </c>
       <c r="D11" t="n">
-        <v>5.669681381608154</v>
+        <v>8.408303357847284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6765407986111105</v>
+        <v>0.1788194444444444</v>
       </c>
       <c r="C12" t="n">
-        <v>1.15700954861111</v>
+        <v>1.420355902777778</v>
       </c>
       <c r="D12" t="n">
-        <v>1.208812669235601</v>
+        <v>6.856968662954126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>sporulation__MP_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3557942708333332</v>
+        <v>-0.07595486111111117</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9018012152777781</v>
+        <v>1.239149305555555</v>
       </c>
       <c r="D13" t="n">
-        <v>3.640784577104901</v>
+        <v>4.348982251933505</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>incubation__spl_end</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3791232638888886</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.017795138888888</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.240119946036906</v>
       </c>
     </row>
   </sheetData>
